--- a/data/dataset_table/cohort_merged.xlsx
+++ b/data/dataset_table/cohort_merged.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muqeemmmm/GitHub/BTReport_v2/data/dataset_table/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959AA7BB-BCE6-FC42-866D-B6FC371E577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-3840" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -4930,8 +4936,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4994,13 +5000,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5038,7 +5052,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -5072,6 +5086,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -5106,9 +5121,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5281,11 +5297,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L647"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="41" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5323,7 +5352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5358,7 +5387,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5393,7 +5422,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5428,7 +5457,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -5463,7 +5492,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5498,7 +5527,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5562,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5568,7 +5597,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -5603,7 +5632,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -5638,7 +5667,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -5673,7 +5702,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -5708,7 +5737,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -5743,7 +5772,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -5778,7 +5807,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -5813,7 +5842,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -5848,7 +5877,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -5883,7 +5912,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -5918,7 +5947,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -5953,7 +5982,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -5988,7 +6017,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -6023,7 +6052,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -6058,7 +6087,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -6093,7 +6122,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -6128,7 +6157,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -6163,7 +6192,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -6198,7 +6227,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -6233,7 +6262,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -6271,7 +6300,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -6309,7 +6338,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -6347,7 +6376,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -6385,7 +6414,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -6423,7 +6452,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -6461,7 +6490,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -6499,7 +6528,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -6534,7 +6563,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -6569,7 +6598,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -6604,7 +6633,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -6642,7 +6671,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -6680,7 +6709,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -6718,7 +6747,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -6756,7 +6785,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -6794,7 +6823,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -6832,7 +6861,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>54</v>
       </c>
@@ -6870,7 +6899,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -6908,7 +6937,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -6943,7 +6972,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>57</v>
       </c>
@@ -6978,7 +7007,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -7013,7 +7042,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -7048,7 +7077,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -7083,7 +7112,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -7118,7 +7147,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -7153,7 +7182,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -7188,7 +7217,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -7223,7 +7252,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -7258,7 +7287,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -7293,7 +7322,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -7328,7 +7357,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -7363,7 +7392,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -7398,7 +7427,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -7433,7 +7462,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -7468,7 +7497,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -7503,7 +7532,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -7538,7 +7567,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -7573,7 +7602,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -7608,7 +7637,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -7628,7 +7657,7 @@
         <v>1624</v>
       </c>
       <c r="G66">
-        <v>79.31999999999999</v>
+        <v>79.319999999999993</v>
       </c>
       <c r="H66" t="s">
         <v>1627</v>
@@ -7643,7 +7672,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -7678,7 +7707,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -7713,7 +7742,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -7748,7 +7777,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -7783,7 +7812,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -7818,7 +7847,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -7853,7 +7882,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -7888,7 +7917,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -7923,7 +7952,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -7958,7 +7987,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -7996,7 +8025,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -8031,7 +8060,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -8066,7 +8095,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -8101,7 +8130,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -8136,7 +8165,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -8171,7 +8200,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -8206,7 +8235,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -8241,7 +8270,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -8276,7 +8305,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -8311,7 +8340,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -8346,7 +8375,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -8381,7 +8410,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -8416,7 +8445,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -8451,7 +8480,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -8471,7 +8500,7 @@
         <v>1625</v>
       </c>
       <c r="G90">
-        <v>79.90000000000001</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="H90" t="s">
         <v>1627</v>
@@ -8486,7 +8515,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -8521,7 +8550,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>102</v>
       </c>
@@ -8541,7 +8570,7 @@
         <v>1624</v>
       </c>
       <c r="G92">
-        <v>72.81999999999999</v>
+        <v>72.819999999999993</v>
       </c>
       <c r="H92" t="s">
         <v>1627</v>
@@ -8556,7 +8585,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>103</v>
       </c>
@@ -8591,7 +8620,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -8626,7 +8655,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -8661,7 +8690,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>106</v>
       </c>
@@ -8681,7 +8710,7 @@
         <v>1625</v>
       </c>
       <c r="G96">
-        <v>66.43000000000001</v>
+        <v>66.430000000000007</v>
       </c>
       <c r="H96" t="s">
         <v>1627</v>
@@ -8696,7 +8725,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>107</v>
       </c>
@@ -8731,7 +8760,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>108</v>
       </c>
@@ -8766,7 +8795,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -8801,7 +8830,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>110</v>
       </c>
@@ -8836,7 +8865,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -8871,7 +8900,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>112</v>
       </c>
@@ -8906,7 +8935,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>113</v>
       </c>
@@ -8941,7 +8970,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -8976,7 +9005,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>115</v>
       </c>
@@ -9011,7 +9040,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>116</v>
       </c>
@@ -9046,7 +9075,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>117</v>
       </c>
@@ -9081,7 +9110,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>118</v>
       </c>
@@ -9116,7 +9145,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>119</v>
       </c>
@@ -9151,7 +9180,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -9186,7 +9215,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>121</v>
       </c>
@@ -9221,7 +9250,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>122</v>
       </c>
@@ -9256,7 +9285,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>123</v>
       </c>
@@ -9291,7 +9320,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>124</v>
       </c>
@@ -9326,7 +9355,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>125</v>
       </c>
@@ -9361,7 +9390,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>126</v>
       </c>
@@ -9396,7 +9425,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>127</v>
       </c>
@@ -9431,7 +9460,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>128</v>
       </c>
@@ -9469,7 +9498,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>129</v>
       </c>
@@ -9507,7 +9536,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>130</v>
       </c>
@@ -9542,7 +9571,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>131</v>
       </c>
@@ -9577,7 +9606,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>132</v>
       </c>
@@ -9612,7 +9641,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>133</v>
       </c>
@@ -9647,7 +9676,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>134</v>
       </c>
@@ -9682,7 +9711,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>135</v>
       </c>
@@ -9717,7 +9746,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>136</v>
       </c>
@@ -9752,7 +9781,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -9787,7 +9816,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -9822,7 +9851,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -9857,7 +9886,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -9892,7 +9921,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>141</v>
       </c>
@@ -9927,7 +9956,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>142</v>
       </c>
@@ -9962,7 +9991,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>143</v>
       </c>
@@ -9997,7 +10026,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>144</v>
       </c>
@@ -10032,7 +10061,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>145</v>
       </c>
@@ -10067,7 +10096,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>146</v>
       </c>
@@ -10102,7 +10131,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>147</v>
       </c>
@@ -10137,7 +10166,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>148</v>
       </c>
@@ -10172,7 +10201,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>149</v>
       </c>
@@ -10207,7 +10236,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>150</v>
       </c>
@@ -10242,7 +10271,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>151</v>
       </c>
@@ -10277,7 +10306,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>152</v>
       </c>
@@ -10312,7 +10341,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>153</v>
       </c>
@@ -10347,7 +10376,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>154</v>
       </c>
@@ -10382,7 +10411,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>155</v>
       </c>
@@ -10417,7 +10446,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>156</v>
       </c>
@@ -10452,7 +10481,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>157</v>
       </c>
@@ -10487,7 +10516,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>158</v>
       </c>
@@ -10522,7 +10551,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>159</v>
       </c>
@@ -10557,7 +10586,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>160</v>
       </c>
@@ -10592,7 +10621,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>161</v>
       </c>
@@ -10627,7 +10656,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>162</v>
       </c>
@@ -10662,7 +10691,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>163</v>
       </c>
@@ -10697,7 +10726,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>164</v>
       </c>
@@ -10732,7 +10761,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>165</v>
       </c>
@@ -10767,7 +10796,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -10802,7 +10831,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>167</v>
       </c>
@@ -10837,7 +10866,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>168</v>
       </c>
@@ -10872,7 +10901,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>169</v>
       </c>
@@ -10907,7 +10936,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>170</v>
       </c>
@@ -10942,7 +10971,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>171</v>
       </c>
@@ -10977,7 +11006,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>172</v>
       </c>
@@ -11012,7 +11041,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>173</v>
       </c>
@@ -11047,7 +11076,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>174</v>
       </c>
@@ -11082,7 +11111,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>175</v>
       </c>
@@ -11120,7 +11149,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>176</v>
       </c>
@@ -11158,7 +11187,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>177</v>
       </c>
@@ -11196,7 +11225,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>178</v>
       </c>
@@ -11234,7 +11263,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>179</v>
       </c>
@@ -11269,7 +11298,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>180</v>
       </c>
@@ -11304,7 +11333,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>181</v>
       </c>
@@ -11339,7 +11368,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>182</v>
       </c>
@@ -11374,7 +11403,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>183</v>
       </c>
@@ -11412,7 +11441,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>184</v>
       </c>
@@ -11450,7 +11479,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>185</v>
       </c>
@@ -11488,7 +11517,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>186</v>
       </c>
@@ -11526,7 +11555,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>187</v>
       </c>
@@ -11564,7 +11593,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="178" spans="1:12">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>188</v>
       </c>
@@ -11602,7 +11631,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="179" spans="1:12">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>189</v>
       </c>
@@ -11640,7 +11669,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="180" spans="1:12">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>190</v>
       </c>
@@ -11678,7 +11707,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="181" spans="1:12">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>191</v>
       </c>
@@ -11713,7 +11742,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>192</v>
       </c>
@@ -11748,7 +11777,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>193</v>
       </c>
@@ -11783,7 +11812,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>194</v>
       </c>
@@ -11818,7 +11847,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>195</v>
       </c>
@@ -11853,7 +11882,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>196</v>
       </c>
@@ -11888,7 +11917,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>197</v>
       </c>
@@ -11923,7 +11952,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>198</v>
       </c>
@@ -11958,7 +11987,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="189" spans="1:12">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -11993,7 +12022,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="190" spans="1:12">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>200</v>
       </c>
@@ -12028,7 +12057,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>201</v>
       </c>
@@ -12063,7 +12092,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>202</v>
       </c>
@@ -12101,7 +12130,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="193" spans="1:12">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>203</v>
       </c>
@@ -12136,7 +12165,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="194" spans="1:12">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>204</v>
       </c>
@@ -12171,7 +12200,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="195" spans="1:12">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>205</v>
       </c>
@@ -12206,7 +12235,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="196" spans="1:12">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>206</v>
       </c>
@@ -12241,7 +12270,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="197" spans="1:12">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>207</v>
       </c>
@@ -12276,7 +12305,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="198" spans="1:12">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>208</v>
       </c>
@@ -12311,7 +12340,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>209</v>
       </c>
@@ -12346,7 +12375,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="200" spans="1:12">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>210</v>
       </c>
@@ -12384,7 +12413,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="201" spans="1:12">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>211</v>
       </c>
@@ -12422,7 +12451,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="202" spans="1:12">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>212</v>
       </c>
@@ -12460,7 +12489,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="203" spans="1:12">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>213</v>
       </c>
@@ -12495,7 +12524,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="204" spans="1:12">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>214</v>
       </c>
@@ -12530,7 +12559,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="205" spans="1:12">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>215</v>
       </c>
@@ -12565,7 +12594,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="206" spans="1:12">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>216</v>
       </c>
@@ -12600,7 +12629,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="207" spans="1:12">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>217</v>
       </c>
@@ -12635,7 +12664,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="208" spans="1:12">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>218</v>
       </c>
@@ -12670,7 +12699,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>219</v>
       </c>
@@ -12705,7 +12734,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="210" spans="1:12">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>220</v>
       </c>
@@ -12740,7 +12769,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="211" spans="1:12">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>221</v>
       </c>
@@ -12775,7 +12804,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="212" spans="1:12">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>222</v>
       </c>
@@ -12810,7 +12839,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="213" spans="1:12">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>223</v>
       </c>
@@ -12845,7 +12874,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="214" spans="1:12">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>224</v>
       </c>
@@ -12880,7 +12909,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="215" spans="1:12">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>225</v>
       </c>
@@ -12918,7 +12947,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="216" spans="1:12">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -12956,7 +12985,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="217" spans="1:12">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>227</v>
       </c>
@@ -12994,7 +13023,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="218" spans="1:12">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>228</v>
       </c>
@@ -13032,7 +13061,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="219" spans="1:12">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>229</v>
       </c>
@@ -13070,7 +13099,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="220" spans="1:12">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>230</v>
       </c>
@@ -13105,7 +13134,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="221" spans="1:12">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>231</v>
       </c>
@@ -13140,7 +13169,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="222" spans="1:12">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>232</v>
       </c>
@@ -13175,7 +13204,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="223" spans="1:12">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>233</v>
       </c>
@@ -13210,7 +13239,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="224" spans="1:12">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>234</v>
       </c>
@@ -13248,7 +13277,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="225" spans="1:12">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>235</v>
       </c>
@@ -13283,7 +13312,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="226" spans="1:12">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>236</v>
       </c>
@@ -13318,7 +13347,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="227" spans="1:12">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>237</v>
       </c>
@@ -13353,7 +13382,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="228" spans="1:12">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>238</v>
       </c>
@@ -13388,7 +13417,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="229" spans="1:12">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>239</v>
       </c>
@@ -13423,7 +13452,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="230" spans="1:12">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>240</v>
       </c>
@@ -13458,7 +13487,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="231" spans="1:12">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>241</v>
       </c>
@@ -13493,7 +13522,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="232" spans="1:12">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>242</v>
       </c>
@@ -13528,7 +13557,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="233" spans="1:12">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>243</v>
       </c>
@@ -13563,7 +13592,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="234" spans="1:12">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>244</v>
       </c>
@@ -13598,7 +13627,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="235" spans="1:12">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>245</v>
       </c>
@@ -13633,7 +13662,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="236" spans="1:12">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>246</v>
       </c>
@@ -13668,7 +13697,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="237" spans="1:12">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>247</v>
       </c>
@@ -13703,7 +13732,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="238" spans="1:12">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>248</v>
       </c>
@@ -13741,7 +13770,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="239" spans="1:12">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>249</v>
       </c>
@@ -13779,7 +13808,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="240" spans="1:12">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>250</v>
       </c>
@@ -13817,7 +13846,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="241" spans="1:12">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>251</v>
       </c>
@@ -13852,7 +13881,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="242" spans="1:12">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>252</v>
       </c>
@@ -13887,7 +13916,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="243" spans="1:12">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>253</v>
       </c>
@@ -13922,7 +13951,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="244" spans="1:12">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>254</v>
       </c>
@@ -13957,7 +13986,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="245" spans="1:12">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>255</v>
       </c>
@@ -13992,7 +14021,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="246" spans="1:12">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>256</v>
       </c>
@@ -14027,7 +14056,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="247" spans="1:12">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>257</v>
       </c>
@@ -14062,7 +14091,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="248" spans="1:12">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>258</v>
       </c>
@@ -14097,7 +14126,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="249" spans="1:12">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>259</v>
       </c>
@@ -14132,7 +14161,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="250" spans="1:12">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>260</v>
       </c>
@@ -14152,7 +14181,7 @@
         <v>1624</v>
       </c>
       <c r="G250">
-        <v>78.20999999999999</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="H250" t="s">
         <v>1627</v>
@@ -14167,7 +14196,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="251" spans="1:12">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>261</v>
       </c>
@@ -14202,7 +14231,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="252" spans="1:12">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>262</v>
       </c>
@@ -14237,7 +14266,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="253" spans="1:12">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>263</v>
       </c>
@@ -14272,7 +14301,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="254" spans="1:12">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>264</v>
       </c>
@@ -14307,7 +14336,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="255" spans="1:12">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>265</v>
       </c>
@@ -14342,7 +14371,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="256" spans="1:12">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>266</v>
       </c>
@@ -14377,7 +14406,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="257" spans="1:12">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>267</v>
       </c>
@@ -14412,7 +14441,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="258" spans="1:12">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>268</v>
       </c>
@@ -14447,7 +14476,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="259" spans="1:12">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>269</v>
       </c>
@@ -14482,7 +14511,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="260" spans="1:12">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>270</v>
       </c>
@@ -14517,7 +14546,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="261" spans="1:12">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>271</v>
       </c>
@@ -14552,7 +14581,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="262" spans="1:12">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>272</v>
       </c>
@@ -14587,7 +14616,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="263" spans="1:12">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>273</v>
       </c>
@@ -14622,7 +14651,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="264" spans="1:12">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>274</v>
       </c>
@@ -14657,7 +14686,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="265" spans="1:12">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>275</v>
       </c>
@@ -14692,7 +14721,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="266" spans="1:12">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>276</v>
       </c>
@@ -14727,7 +14756,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="267" spans="1:12">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>277</v>
       </c>
@@ -14762,7 +14791,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="268" spans="1:12">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>278</v>
       </c>
@@ -14797,7 +14826,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="269" spans="1:12">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>279</v>
       </c>
@@ -14832,7 +14861,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="270" spans="1:12">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>280</v>
       </c>
@@ -14867,7 +14896,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="271" spans="1:12">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>281</v>
       </c>
@@ -14902,7 +14931,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="272" spans="1:12">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>282</v>
       </c>
@@ -14937,7 +14966,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="273" spans="1:12">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>283</v>
       </c>
@@ -14972,7 +15001,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="274" spans="1:12">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>284</v>
       </c>
@@ -15007,7 +15036,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="275" spans="1:12">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>285</v>
       </c>
@@ -15042,7 +15071,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="276" spans="1:12">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>286</v>
       </c>
@@ -15077,7 +15106,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="277" spans="1:12">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>287</v>
       </c>
@@ -15112,7 +15141,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="278" spans="1:12">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>288</v>
       </c>
@@ -15147,7 +15176,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="279" spans="1:12">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>289</v>
       </c>
@@ -15182,7 +15211,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="280" spans="1:12">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>290</v>
       </c>
@@ -15217,7 +15246,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="281" spans="1:12">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>291</v>
       </c>
@@ -15255,7 +15284,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="282" spans="1:12">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>292</v>
       </c>
@@ -15293,7 +15322,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="283" spans="1:12">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>293</v>
       </c>
@@ -15331,7 +15360,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="284" spans="1:12">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>294</v>
       </c>
@@ -15369,7 +15398,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="285" spans="1:12">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>295</v>
       </c>
@@ -15407,7 +15436,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="286" spans="1:12">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>296</v>
       </c>
@@ -15445,7 +15474,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="287" spans="1:12">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>297</v>
       </c>
@@ -15483,7 +15512,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="288" spans="1:12">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>298</v>
       </c>
@@ -15521,7 +15550,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="289" spans="1:12">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>299</v>
       </c>
@@ -15556,7 +15585,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="290" spans="1:12">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>300</v>
       </c>
@@ -15591,7 +15620,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="291" spans="1:12">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>301</v>
       </c>
@@ -15626,7 +15655,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="292" spans="1:12">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>302</v>
       </c>
@@ -15661,7 +15690,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="293" spans="1:12">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>303</v>
       </c>
@@ -15696,7 +15725,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="294" spans="1:12">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>304</v>
       </c>
@@ -15734,7 +15763,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="295" spans="1:12">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>305</v>
       </c>
@@ -15772,7 +15801,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="296" spans="1:12">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>306</v>
       </c>
@@ -15807,7 +15836,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="297" spans="1:12">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>307</v>
       </c>
@@ -15842,7 +15871,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="298" spans="1:12">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>308</v>
       </c>
@@ -15877,7 +15906,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="299" spans="1:12">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>309</v>
       </c>
@@ -15912,7 +15941,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="300" spans="1:12">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>310</v>
       </c>
@@ -15947,7 +15976,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="301" spans="1:12">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>311</v>
       </c>
@@ -15982,7 +16011,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="302" spans="1:12">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>312</v>
       </c>
@@ -16017,7 +16046,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="303" spans="1:12">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>313</v>
       </c>
@@ -16052,7 +16081,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="304" spans="1:12">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>314</v>
       </c>
@@ -16087,7 +16116,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="305" spans="1:12">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>315</v>
       </c>
@@ -16122,7 +16151,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="306" spans="1:12">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>316</v>
       </c>
@@ -16157,7 +16186,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="307" spans="1:12">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>317</v>
       </c>
@@ -16192,7 +16221,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="308" spans="1:12">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>318</v>
       </c>
@@ -16227,7 +16256,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="309" spans="1:12">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>319</v>
       </c>
@@ -16262,7 +16291,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="310" spans="1:12">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>320</v>
       </c>
@@ -16297,7 +16326,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="311" spans="1:12">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>321</v>
       </c>
@@ -16335,7 +16364,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="312" spans="1:12">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>322</v>
       </c>
@@ -16370,7 +16399,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="313" spans="1:12">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>323</v>
       </c>
@@ -16405,7 +16434,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="314" spans="1:12">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>324</v>
       </c>
@@ -16440,7 +16469,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="315" spans="1:12">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>325</v>
       </c>
@@ -16475,7 +16504,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="316" spans="1:12">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>326</v>
       </c>
@@ -16495,7 +16524,7 @@
         <v>1624</v>
       </c>
       <c r="G316">
-        <v>76.15000000000001</v>
+        <v>76.150000000000006</v>
       </c>
       <c r="H316" t="s">
         <v>1627</v>
@@ -16510,7 +16539,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="317" spans="1:12">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>327</v>
       </c>
@@ -16545,7 +16574,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="318" spans="1:12">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>328</v>
       </c>
@@ -16580,7 +16609,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="319" spans="1:12">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>329</v>
       </c>
@@ -16615,7 +16644,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="320" spans="1:12">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>330</v>
       </c>
@@ -16653,7 +16682,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="321" spans="1:12">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>331</v>
       </c>
@@ -16691,7 +16720,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="322" spans="1:12">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>332</v>
       </c>
@@ -16726,7 +16755,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="323" spans="1:12">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>333</v>
       </c>
@@ -16764,7 +16793,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="324" spans="1:12">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>334</v>
       </c>
@@ -16799,7 +16828,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="325" spans="1:12">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>335</v>
       </c>
@@ -16834,7 +16863,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="326" spans="1:12">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>336</v>
       </c>
@@ -16869,7 +16898,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="327" spans="1:12">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>337</v>
       </c>
@@ -16904,7 +16933,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="328" spans="1:12">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>338</v>
       </c>
@@ -16939,7 +16968,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="329" spans="1:12">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>339</v>
       </c>
@@ -16974,7 +17003,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="330" spans="1:12">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>340</v>
       </c>
@@ -17009,7 +17038,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="331" spans="1:12">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>341</v>
       </c>
@@ -17044,7 +17073,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="332" spans="1:12">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>342</v>
       </c>
@@ -17079,7 +17108,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="333" spans="1:12">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>343</v>
       </c>
@@ -17114,7 +17143,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="334" spans="1:12">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>344</v>
       </c>
@@ -17152,7 +17181,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="335" spans="1:12">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>345</v>
       </c>
@@ -17190,7 +17219,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="336" spans="1:12">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>346</v>
       </c>
@@ -17228,7 +17257,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="337" spans="1:12">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>347</v>
       </c>
@@ -17263,7 +17292,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="338" spans="1:12">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>348</v>
       </c>
@@ -17298,7 +17327,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="339" spans="1:12">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>349</v>
       </c>
@@ -17333,7 +17362,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="340" spans="1:12">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>350</v>
       </c>
@@ -17368,7 +17397,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="341" spans="1:12">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>351</v>
       </c>
@@ -17403,7 +17432,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="342" spans="1:12">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>352</v>
       </c>
@@ -17438,7 +17467,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="343" spans="1:12">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>353</v>
       </c>
@@ -17473,7 +17502,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="344" spans="1:12">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>354</v>
       </c>
@@ -17508,7 +17537,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="345" spans="1:12">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>355</v>
       </c>
@@ -17543,7 +17572,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="346" spans="1:12">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>356</v>
       </c>
@@ -17578,7 +17607,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="347" spans="1:12">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>357</v>
       </c>
@@ -17613,7 +17642,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="348" spans="1:12">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>358</v>
       </c>
@@ -17648,7 +17677,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="349" spans="1:12">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>359</v>
       </c>
@@ -17683,7 +17712,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="350" spans="1:12">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>360</v>
       </c>
@@ -17718,7 +17747,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="351" spans="1:12">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>361</v>
       </c>
@@ -17753,7 +17782,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="352" spans="1:12">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>362</v>
       </c>
@@ -17788,7 +17817,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="353" spans="1:12">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>363</v>
       </c>
@@ -17823,7 +17852,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="354" spans="1:12">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>364</v>
       </c>
@@ -17858,7 +17887,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="355" spans="1:12">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>365</v>
       </c>
@@ -17893,7 +17922,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="356" spans="1:12">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>366</v>
       </c>
@@ -17931,7 +17960,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="357" spans="1:12">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>367</v>
       </c>
@@ -17966,7 +17995,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="358" spans="1:12">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>368</v>
       </c>
@@ -18001,7 +18030,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="359" spans="1:12">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>369</v>
       </c>
@@ -18021,7 +18050,7 @@
         <v>1625</v>
       </c>
       <c r="G359">
-        <v>71.65000000000001</v>
+        <v>71.650000000000006</v>
       </c>
       <c r="H359" t="s">
         <v>1627</v>
@@ -18036,7 +18065,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="360" spans="1:12">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>370</v>
       </c>
@@ -18071,7 +18100,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="361" spans="1:12">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>371</v>
       </c>
@@ -18106,7 +18135,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="362" spans="1:12">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>372</v>
       </c>
@@ -18141,7 +18170,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="363" spans="1:12">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>373</v>
       </c>
@@ -18176,7 +18205,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="364" spans="1:12">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>374</v>
       </c>
@@ -18211,7 +18240,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="365" spans="1:12">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>375</v>
       </c>
@@ -18246,7 +18275,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="366" spans="1:12">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>376</v>
       </c>
@@ -18284,7 +18313,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="367" spans="1:12">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>377</v>
       </c>
@@ -18319,7 +18348,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="368" spans="1:12">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>378</v>
       </c>
@@ -18354,7 +18383,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="369" spans="1:12">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>379</v>
       </c>
@@ -18389,7 +18418,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="370" spans="1:12">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>380</v>
       </c>
@@ -18424,7 +18453,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="371" spans="1:12">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>381</v>
       </c>
@@ -18459,7 +18488,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="372" spans="1:12">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>382</v>
       </c>
@@ -18494,7 +18523,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="373" spans="1:12">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>383</v>
       </c>
@@ -18529,7 +18558,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="374" spans="1:12">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>384</v>
       </c>
@@ -18564,7 +18593,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="375" spans="1:12">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>385</v>
       </c>
@@ -18599,7 +18628,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="376" spans="1:12">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>386</v>
       </c>
@@ -18634,7 +18663,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="377" spans="1:12">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>387</v>
       </c>
@@ -18672,7 +18701,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="378" spans="1:12">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>388</v>
       </c>
@@ -18710,7 +18739,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="379" spans="1:12">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>389</v>
       </c>
@@ -18745,7 +18774,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="380" spans="1:12">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>390</v>
       </c>
@@ -18780,7 +18809,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="381" spans="1:12">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>391</v>
       </c>
@@ -18815,7 +18844,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="382" spans="1:12">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>392</v>
       </c>
@@ -18850,7 +18879,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="383" spans="1:12">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>393</v>
       </c>
@@ -18885,7 +18914,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="384" spans="1:12">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>394</v>
       </c>
@@ -18920,7 +18949,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="385" spans="1:12">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>395</v>
       </c>
@@ -18955,7 +18984,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="386" spans="1:12">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>396</v>
       </c>
@@ -18990,7 +19019,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="387" spans="1:12">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>397</v>
       </c>
@@ -19025,7 +19054,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="388" spans="1:12">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>398</v>
       </c>
@@ -19060,7 +19089,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="389" spans="1:12">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>399</v>
       </c>
@@ -19095,7 +19124,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="390" spans="1:12">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>400</v>
       </c>
@@ -19130,7 +19159,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="391" spans="1:12">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>401</v>
       </c>
@@ -19165,7 +19194,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="392" spans="1:12">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>402</v>
       </c>
@@ -19200,7 +19229,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="393" spans="1:12">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>403</v>
       </c>
@@ -19235,7 +19264,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="394" spans="1:12">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>404</v>
       </c>
@@ -19273,7 +19302,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="395" spans="1:12">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>405</v>
       </c>
@@ -19308,7 +19337,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="396" spans="1:12">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>406</v>
       </c>
@@ -19343,7 +19372,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="397" spans="1:12">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>407</v>
       </c>
@@ -19378,7 +19407,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="398" spans="1:12">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>408</v>
       </c>
@@ -19413,7 +19442,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="399" spans="1:12">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>409</v>
       </c>
@@ -19448,7 +19477,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="400" spans="1:12">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>410</v>
       </c>
@@ -19483,7 +19512,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="401" spans="1:12">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>411</v>
       </c>
@@ -19518,7 +19547,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="402" spans="1:12">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>412</v>
       </c>
@@ -19553,7 +19582,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="403" spans="1:12">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>413</v>
       </c>
@@ -19588,7 +19617,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="404" spans="1:12">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>414</v>
       </c>
@@ -19623,7 +19652,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="405" spans="1:12">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>415</v>
       </c>
@@ -19658,7 +19687,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="406" spans="1:12">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>416</v>
       </c>
@@ -19693,7 +19722,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="407" spans="1:12">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>417</v>
       </c>
@@ -19728,7 +19757,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="408" spans="1:12">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>418</v>
       </c>
@@ -19763,7 +19792,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="409" spans="1:12">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>419</v>
       </c>
@@ -19798,7 +19827,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="410" spans="1:12">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>420</v>
       </c>
@@ -19833,7 +19862,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="411" spans="1:12">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>421</v>
       </c>
@@ -19868,7 +19897,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="412" spans="1:12">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>422</v>
       </c>
@@ -19903,7 +19932,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="413" spans="1:12">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>423</v>
       </c>
@@ -19941,7 +19970,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="414" spans="1:12">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>424</v>
       </c>
@@ -19979,7 +20008,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="415" spans="1:12">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>425</v>
       </c>
@@ -20017,7 +20046,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="416" spans="1:12">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>426</v>
       </c>
@@ -20055,7 +20084,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="417" spans="1:12">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>427</v>
       </c>
@@ -20093,7 +20122,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="418" spans="1:12">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>428</v>
       </c>
@@ -20131,7 +20160,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="419" spans="1:12">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>429</v>
       </c>
@@ -20169,7 +20198,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="420" spans="1:12">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>430</v>
       </c>
@@ -20207,7 +20236,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="421" spans="1:12">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>431</v>
       </c>
@@ -20245,7 +20274,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="422" spans="1:12">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>432</v>
       </c>
@@ -20283,7 +20312,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="423" spans="1:12">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>433</v>
       </c>
@@ -20321,7 +20350,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="424" spans="1:12">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>434</v>
       </c>
@@ -20359,7 +20388,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="425" spans="1:12">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>435</v>
       </c>
@@ -20394,7 +20423,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="426" spans="1:12">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>436</v>
       </c>
@@ -20429,7 +20458,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="427" spans="1:12">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>437</v>
       </c>
@@ -20464,7 +20493,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="428" spans="1:12">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>438</v>
       </c>
@@ -20499,7 +20528,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="429" spans="1:12">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>439</v>
       </c>
@@ -20534,7 +20563,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="430" spans="1:12">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>440</v>
       </c>
@@ -20569,7 +20598,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="431" spans="1:12">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>441</v>
       </c>
@@ -20604,7 +20633,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="432" spans="1:12">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>442</v>
       </c>
@@ -20639,7 +20668,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="433" spans="1:12">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>443</v>
       </c>
@@ -20674,7 +20703,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="434" spans="1:12">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>444</v>
       </c>
@@ -20709,7 +20738,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="435" spans="1:12">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>445</v>
       </c>
@@ -20744,7 +20773,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="436" spans="1:12">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>446</v>
       </c>
@@ -20779,7 +20808,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="437" spans="1:12">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>447</v>
       </c>
@@ -20814,7 +20843,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="438" spans="1:12">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>448</v>
       </c>
@@ -20849,7 +20878,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="439" spans="1:12">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>449</v>
       </c>
@@ -20884,7 +20913,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="440" spans="1:12">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>450</v>
       </c>
@@ -20919,7 +20948,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="441" spans="1:12">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>451</v>
       </c>
@@ -20957,7 +20986,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="442" spans="1:12">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>452</v>
       </c>
@@ -20995,7 +21024,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="443" spans="1:12">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>453</v>
       </c>
@@ -21033,7 +21062,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="444" spans="1:12">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>454</v>
       </c>
@@ -21068,7 +21097,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="445" spans="1:12">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>455</v>
       </c>
@@ -21103,7 +21132,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="446" spans="1:12">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>456</v>
       </c>
@@ -21138,7 +21167,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="447" spans="1:12">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>457</v>
       </c>
@@ -21173,7 +21202,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="448" spans="1:12">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>458</v>
       </c>
@@ -21208,7 +21237,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="449" spans="1:12">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>459</v>
       </c>
@@ -21243,7 +21272,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="450" spans="1:12">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>460</v>
       </c>
@@ -21278,7 +21307,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="451" spans="1:12">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>461</v>
       </c>
@@ -21313,7 +21342,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="452" spans="1:12">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>462</v>
       </c>
@@ -21348,7 +21377,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="453" spans="1:12">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>463</v>
       </c>
@@ -21383,7 +21412,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="454" spans="1:12">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>464</v>
       </c>
@@ -21418,7 +21447,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="455" spans="1:12">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>465</v>
       </c>
@@ -21453,7 +21482,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="456" spans="1:12">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>466</v>
       </c>
@@ -21488,7 +21517,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="457" spans="1:12">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>467</v>
       </c>
@@ -21523,7 +21552,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="458" spans="1:12">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>468</v>
       </c>
@@ -21558,7 +21587,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="459" spans="1:12">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>469</v>
       </c>
@@ -21593,7 +21622,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="460" spans="1:12">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>470</v>
       </c>
@@ -21628,7 +21657,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="461" spans="1:12">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>471</v>
       </c>
@@ -21663,7 +21692,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="462" spans="1:12">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>472</v>
       </c>
@@ -21698,7 +21727,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="463" spans="1:12">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>473</v>
       </c>
@@ -21733,7 +21762,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="464" spans="1:12">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>474</v>
       </c>
@@ -21768,7 +21797,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="465" spans="1:12">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>475</v>
       </c>
@@ -21803,7 +21832,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="466" spans="1:12">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>476</v>
       </c>
@@ -21838,7 +21867,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="467" spans="1:12">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>477</v>
       </c>
@@ -21873,7 +21902,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="468" spans="1:12">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>478</v>
       </c>
@@ -21908,7 +21937,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="469" spans="1:12">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>479</v>
       </c>
@@ -21943,7 +21972,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="470" spans="1:12">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>480</v>
       </c>
@@ -21978,7 +22007,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="471" spans="1:12">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>481</v>
       </c>
@@ -22013,7 +22042,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="472" spans="1:12">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>482</v>
       </c>
@@ -22048,7 +22077,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="473" spans="1:12">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>483</v>
       </c>
@@ -22086,7 +22115,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="474" spans="1:12">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>484</v>
       </c>
@@ -22124,7 +22153,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="475" spans="1:12">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>485</v>
       </c>
@@ -22159,7 +22188,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="476" spans="1:12">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>486</v>
       </c>
@@ -22194,7 +22223,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="477" spans="1:12">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>487</v>
       </c>
@@ -22229,7 +22258,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="478" spans="1:12">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>488</v>
       </c>
@@ -22264,7 +22293,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="479" spans="1:12">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>489</v>
       </c>
@@ -22299,7 +22328,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="480" spans="1:12">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>490</v>
       </c>
@@ -22334,7 +22363,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="481" spans="1:12">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>491</v>
       </c>
@@ -22369,7 +22398,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="482" spans="1:12">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>492</v>
       </c>
@@ -22404,7 +22433,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="483" spans="1:12">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>493</v>
       </c>
@@ -22439,7 +22468,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="484" spans="1:12">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>494</v>
       </c>
@@ -22474,7 +22503,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="485" spans="1:12">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>495</v>
       </c>
@@ -22494,7 +22523,7 @@
         <v>1625</v>
       </c>
       <c r="G485">
-        <v>68.95999999999999</v>
+        <v>68.959999999999994</v>
       </c>
       <c r="H485" t="s">
         <v>1627</v>
@@ -22509,7 +22538,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="486" spans="1:12">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>496</v>
       </c>
@@ -22544,7 +22573,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="487" spans="1:12">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>497</v>
       </c>
@@ -22579,7 +22608,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="488" spans="1:12">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>498</v>
       </c>
@@ -22614,7 +22643,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="489" spans="1:12">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>499</v>
       </c>
@@ -22649,7 +22678,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="490" spans="1:12">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>500</v>
       </c>
@@ -22684,7 +22713,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="491" spans="1:12">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>501</v>
       </c>
@@ -22719,7 +22748,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="492" spans="1:12">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>502</v>
       </c>
@@ -22754,7 +22783,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="493" spans="1:12">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>503</v>
       </c>
@@ -22789,7 +22818,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="494" spans="1:12">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>504</v>
       </c>
@@ -22827,7 +22856,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="495" spans="1:12">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>505</v>
       </c>
@@ -22862,7 +22891,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="496" spans="1:12">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>506</v>
       </c>
@@ -22897,7 +22926,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="497" spans="1:12">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>507</v>
       </c>
@@ -22932,7 +22961,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="498" spans="1:12">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>508</v>
       </c>
@@ -22967,7 +22996,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="499" spans="1:12">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>509</v>
       </c>
@@ -23005,7 +23034,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="500" spans="1:12">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>510</v>
       </c>
@@ -23040,7 +23069,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="501" spans="1:12">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>511</v>
       </c>
@@ -23075,7 +23104,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="502" spans="1:12">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>512</v>
       </c>
@@ -23110,7 +23139,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="503" spans="1:12">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>513</v>
       </c>
@@ -23145,7 +23174,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="504" spans="1:12">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>514</v>
       </c>
@@ -23180,7 +23209,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="505" spans="1:12">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>515</v>
       </c>
@@ -23215,7 +23244,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="506" spans="1:12">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>516</v>
       </c>
@@ -23250,7 +23279,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="507" spans="1:12">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>517</v>
       </c>
@@ -23285,7 +23314,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="508" spans="1:12">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>518</v>
       </c>
@@ -23320,7 +23349,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="509" spans="1:12">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>519</v>
       </c>
@@ -23355,7 +23384,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="510" spans="1:12">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>520</v>
       </c>
@@ -23390,7 +23419,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="511" spans="1:12">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>521</v>
       </c>
@@ -23425,7 +23454,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="512" spans="1:12">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>522</v>
       </c>
@@ -23460,7 +23489,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="513" spans="1:12">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>523</v>
       </c>
@@ -23495,7 +23524,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="514" spans="1:12">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>524</v>
       </c>
@@ -23530,7 +23559,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="515" spans="1:12">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>525</v>
       </c>
@@ -23565,7 +23594,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="516" spans="1:12">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>526</v>
       </c>
@@ -23600,7 +23629,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="517" spans="1:12">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>527</v>
       </c>
@@ -23635,7 +23664,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="518" spans="1:12">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>528</v>
       </c>
@@ -23670,7 +23699,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="519" spans="1:12">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>529</v>
       </c>
@@ -23705,7 +23734,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="520" spans="1:12">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>530</v>
       </c>
@@ -23740,7 +23769,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="521" spans="1:12">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>531</v>
       </c>
@@ -23775,7 +23804,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="522" spans="1:12">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>532</v>
       </c>
@@ -23810,7 +23839,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="523" spans="1:12">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>533</v>
       </c>
@@ -23845,7 +23874,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="524" spans="1:12">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>534</v>
       </c>
@@ -23880,7 +23909,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="525" spans="1:12">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>535</v>
       </c>
@@ -23915,7 +23944,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="526" spans="1:12">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>536</v>
       </c>
@@ -23950,7 +23979,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="527" spans="1:12">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>537</v>
       </c>
@@ -23985,7 +24014,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="528" spans="1:12">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>538</v>
       </c>
@@ -24020,7 +24049,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="529" spans="1:12">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>539</v>
       </c>
@@ -24055,7 +24084,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="530" spans="1:12">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>540</v>
       </c>
@@ -24090,7 +24119,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="531" spans="1:12">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>541</v>
       </c>
@@ -24125,7 +24154,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="532" spans="1:12">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>542</v>
       </c>
@@ -24160,7 +24189,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="533" spans="1:12">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>543</v>
       </c>
@@ -24195,7 +24224,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="534" spans="1:12">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>544</v>
       </c>
@@ -24230,7 +24259,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="535" spans="1:12">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>545</v>
       </c>
@@ -24265,7 +24294,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="536" spans="1:12">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>546</v>
       </c>
@@ -24300,7 +24329,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="537" spans="1:12">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>547</v>
       </c>
@@ -24335,7 +24364,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="538" spans="1:12">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>548</v>
       </c>
@@ -24370,7 +24399,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="539" spans="1:12">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>549</v>
       </c>
@@ -24408,7 +24437,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="540" spans="1:12">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>550</v>
       </c>
@@ -24446,7 +24475,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="541" spans="1:12">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>551</v>
       </c>
@@ -24484,7 +24513,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="542" spans="1:12">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>552</v>
       </c>
@@ -24522,7 +24551,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="543" spans="1:12">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>553</v>
       </c>
@@ -24560,7 +24589,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="544" spans="1:12">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>554</v>
       </c>
@@ -24595,7 +24624,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="545" spans="1:12">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>555</v>
       </c>
@@ -24630,7 +24659,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="546" spans="1:12">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>556</v>
       </c>
@@ -24665,7 +24694,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="547" spans="1:12">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>557</v>
       </c>
@@ -24700,7 +24729,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="548" spans="1:12">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>558</v>
       </c>
@@ -24735,7 +24764,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="549" spans="1:12">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>559</v>
       </c>
@@ -24770,7 +24799,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="550" spans="1:12">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>560</v>
       </c>
@@ -24805,7 +24834,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="551" spans="1:12">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>561</v>
       </c>
@@ -24840,7 +24869,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="552" spans="1:12">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>562</v>
       </c>
@@ -24878,7 +24907,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="553" spans="1:12">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>563</v>
       </c>
@@ -24916,7 +24945,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="554" spans="1:12">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>564</v>
       </c>
@@ -24954,7 +24983,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="555" spans="1:12">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>565</v>
       </c>
@@ -24989,7 +25018,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="556" spans="1:12">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>566</v>
       </c>
@@ -25024,7 +25053,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="557" spans="1:12">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>567</v>
       </c>
@@ -25059,7 +25088,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="558" spans="1:12">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>568</v>
       </c>
@@ -25094,7 +25123,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="559" spans="1:12">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>569</v>
       </c>
@@ -25129,7 +25158,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="560" spans="1:12">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>570</v>
       </c>
@@ -25164,7 +25193,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="561" spans="1:12">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>571</v>
       </c>
@@ -25199,7 +25228,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="562" spans="1:12">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>572</v>
       </c>
@@ -25234,7 +25263,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="563" spans="1:12">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>573</v>
       </c>
@@ -25269,7 +25298,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="564" spans="1:12">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>574</v>
       </c>
@@ -25304,7 +25333,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="565" spans="1:12">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>575</v>
       </c>
@@ -25339,7 +25368,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="566" spans="1:12">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>576</v>
       </c>
@@ -25374,7 +25403,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="567" spans="1:12">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>577</v>
       </c>
@@ -25409,7 +25438,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="568" spans="1:12">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>578</v>
       </c>
@@ -25444,7 +25473,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="569" spans="1:12">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>579</v>
       </c>
@@ -25479,7 +25508,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="570" spans="1:12">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>580</v>
       </c>
@@ -25514,7 +25543,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="571" spans="1:12">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>581</v>
       </c>
@@ -25549,7 +25578,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="572" spans="1:12">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>582</v>
       </c>
@@ -25584,7 +25613,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="573" spans="1:12">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>583</v>
       </c>
@@ -25619,7 +25648,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="574" spans="1:12">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>584</v>
       </c>
@@ -25654,7 +25683,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="575" spans="1:12">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>585</v>
       </c>
@@ -25689,7 +25718,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="576" spans="1:12">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>586</v>
       </c>
@@ -25724,7 +25753,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="577" spans="1:12">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>587</v>
       </c>
@@ -25759,7 +25788,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="578" spans="1:12">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>588</v>
       </c>
@@ -25794,7 +25823,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="579" spans="1:12">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>589</v>
       </c>
@@ -25829,7 +25858,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="580" spans="1:12">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>590</v>
       </c>
@@ -25849,7 +25878,7 @@
         <v>1624</v>
       </c>
       <c r="G580">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="H580" t="s">
         <v>1627</v>
@@ -25864,7 +25893,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="581" spans="1:12">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>591</v>
       </c>
@@ -25899,7 +25928,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="582" spans="1:12">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>592</v>
       </c>
@@ -25934,7 +25963,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="583" spans="1:12">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>593</v>
       </c>
@@ -25969,7 +25998,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="584" spans="1:12">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>594</v>
       </c>
@@ -26004,7 +26033,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="585" spans="1:12">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>595</v>
       </c>
@@ -26039,7 +26068,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="586" spans="1:12">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>596</v>
       </c>
@@ -26074,7 +26103,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="587" spans="1:12">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>597</v>
       </c>
@@ -26109,7 +26138,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="588" spans="1:12">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>598</v>
       </c>
@@ -26147,7 +26176,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="589" spans="1:12">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>599</v>
       </c>
@@ -26185,7 +26214,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="590" spans="1:12">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>600</v>
       </c>
@@ -26223,7 +26252,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="591" spans="1:12">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>601</v>
       </c>
@@ -26261,7 +26290,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="592" spans="1:12">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>602</v>
       </c>
@@ -26299,7 +26328,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="593" spans="1:12">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>603</v>
       </c>
@@ -26337,7 +26366,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="594" spans="1:12">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>604</v>
       </c>
@@ -26375,7 +26404,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="595" spans="1:12">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>605</v>
       </c>
@@ -26413,7 +26442,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="596" spans="1:12">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>606</v>
       </c>
@@ -26451,7 +26480,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="597" spans="1:12">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>607</v>
       </c>
@@ -26489,7 +26518,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="598" spans="1:12">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>608</v>
       </c>
@@ -26524,7 +26553,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="599" spans="1:12">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>609</v>
       </c>
@@ -26559,7 +26588,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="600" spans="1:12">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>610</v>
       </c>
@@ -26594,7 +26623,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="601" spans="1:12">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>611</v>
       </c>
@@ -26629,7 +26658,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="602" spans="1:12">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>612</v>
       </c>
@@ -26667,7 +26696,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="603" spans="1:12">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>613</v>
       </c>
@@ -26705,7 +26734,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="604" spans="1:12">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>614</v>
       </c>
@@ -26740,7 +26769,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="605" spans="1:12">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>615</v>
       </c>
@@ -26775,7 +26804,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="606" spans="1:12">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>616</v>
       </c>
@@ -26810,7 +26839,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="607" spans="1:12">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>617</v>
       </c>
@@ -26845,7 +26874,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="608" spans="1:12">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>618</v>
       </c>
@@ -26880,7 +26909,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="609" spans="1:12">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>619</v>
       </c>
@@ -26915,7 +26944,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="610" spans="1:12">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>620</v>
       </c>
@@ -26950,7 +26979,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="611" spans="1:12">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>621</v>
       </c>
@@ -26985,7 +27014,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="612" spans="1:12">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>622</v>
       </c>
@@ -27020,7 +27049,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="613" spans="1:12">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>623</v>
       </c>
@@ -27055,7 +27084,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="614" spans="1:12">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>624</v>
       </c>
@@ -27093,7 +27122,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="615" spans="1:12">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>625</v>
       </c>
@@ -27131,7 +27160,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="616" spans="1:12">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>626</v>
       </c>
@@ -27166,7 +27195,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="617" spans="1:12">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>627</v>
       </c>
@@ -27201,7 +27230,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="618" spans="1:12">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>628</v>
       </c>
@@ -27221,7 +27250,7 @@
         <v>1624</v>
       </c>
       <c r="G618">
-        <v>64.76000000000001</v>
+        <v>64.760000000000005</v>
       </c>
       <c r="H618" t="s">
         <v>1627</v>
@@ -27236,7 +27265,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="619" spans="1:12">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>629</v>
       </c>
@@ -27271,7 +27300,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="620" spans="1:12">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>630</v>
       </c>
@@ -27306,7 +27335,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="621" spans="1:12">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>631</v>
       </c>
@@ -27344,7 +27373,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="622" spans="1:12">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>632</v>
       </c>
@@ -27379,7 +27408,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="623" spans="1:12">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>633</v>
       </c>
@@ -27414,7 +27443,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="624" spans="1:12">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>634</v>
       </c>
@@ -27449,7 +27478,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="625" spans="1:12">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>635</v>
       </c>
@@ -27484,7 +27513,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="626" spans="1:12">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>636</v>
       </c>
@@ -27519,7 +27548,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="627" spans="1:12">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>637</v>
       </c>
@@ -27554,7 +27583,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="628" spans="1:12">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>638</v>
       </c>
@@ -27589,7 +27618,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="629" spans="1:12">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>639</v>
       </c>
@@ -27624,7 +27653,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="630" spans="1:12">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>640</v>
       </c>
@@ -27659,7 +27688,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="631" spans="1:12">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>641</v>
       </c>
@@ -27694,7 +27723,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="632" spans="1:12">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>642</v>
       </c>
@@ -27729,7 +27758,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="633" spans="1:12">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>643</v>
       </c>
@@ -27764,7 +27793,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="634" spans="1:12">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>644</v>
       </c>
@@ -27799,7 +27828,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="635" spans="1:12">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>645</v>
       </c>
@@ -27834,7 +27863,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="636" spans="1:12">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>646</v>
       </c>
@@ -27869,7 +27898,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="637" spans="1:12">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>647</v>
       </c>
@@ -27904,7 +27933,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="638" spans="1:12">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>648</v>
       </c>
@@ -27939,7 +27968,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="639" spans="1:12">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>649</v>
       </c>
@@ -27974,7 +28003,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="640" spans="1:12">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>650</v>
       </c>
@@ -28009,7 +28038,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="641" spans="1:12">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>651</v>
       </c>
@@ -28044,7 +28073,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="642" spans="1:12">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>652</v>
       </c>
@@ -28079,7 +28108,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="643" spans="1:12">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>653</v>
       </c>
@@ -28117,7 +28146,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="644" spans="1:12">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>654</v>
       </c>
@@ -28152,7 +28181,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="645" spans="1:12">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>655</v>
       </c>
@@ -28187,7 +28216,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="646" spans="1:12">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>656</v>
       </c>
@@ -28222,7 +28251,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="647" spans="1:12">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>657</v>
       </c>
